--- a/Test upload format/MSME/NewCGMSME.xlsx
+++ b/Test upload format/MSME/NewCGMSME.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="139">
   <si>
     <t>UnitName</t>
   </si>
@@ -131,6 +131,9 @@
     <t>UDYAM-QA-44-7123401</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>test</t>
   </si>
   <si>
@@ -143,7 +146,10 @@
     <t>01</t>
   </si>
   <si>
-    <t>QAMSME01</t>
+    <t>Acust01</t>
+  </si>
+  <si>
+    <t>Aloan01</t>
   </si>
   <si>
     <t>26-06-2026</t>
@@ -161,7 +167,13 @@
     <t>UDYAM-QA-44-7123402</t>
   </si>
   <si>
-    <t>QAMSME02</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Acust02</t>
+  </si>
+  <si>
+    <t>Aloan02</t>
   </si>
   <si>
     <t>someshN</t>
@@ -173,7 +185,10 @@
     <t>UDYAM-QA-44-7123403</t>
   </si>
   <si>
-    <t>QAMSME03</t>
+    <t>Acust03</t>
+  </si>
+  <si>
+    <t>Aloan03</t>
   </si>
   <si>
     <t>somesho</t>
@@ -182,52 +197,64 @@
     <t>XMJPS6604Q</t>
   </si>
   <si>
+    <t>UDYAM-QA-44-7123404</t>
+  </si>
+  <si>
+    <t>Acust04</t>
+  </si>
+  <si>
+    <t>Aloan04</t>
+  </si>
+  <si>
+    <t>XMJPS6605Q</t>
+  </si>
+  <si>
+    <t>UDYAM-QA-44-7123405</t>
+  </si>
+  <si>
+    <t>Acust05</t>
+  </si>
+  <si>
+    <t>Aloan05</t>
+  </si>
+  <si>
+    <t>XMJPS6606Q</t>
+  </si>
+  <si>
+    <t>UDYAM-QA-44-7123406</t>
+  </si>
+  <si>
+    <t>Acust06</t>
+  </si>
+  <si>
+    <t>Aloan06</t>
+  </si>
+  <si>
+    <t>XMJPS6607Q</t>
+  </si>
+  <si>
+    <t>UDYAM-QA-44-7123407</t>
+  </si>
+  <si>
+    <t>Acust07</t>
+  </si>
+  <si>
+    <t>Aloan07</t>
+  </si>
+  <si>
+    <t>XMJPS6608Q</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>UDYAM-QA-44-7123404</t>
-  </si>
-  <si>
-    <t>QAMSME04</t>
-  </si>
-  <si>
-    <t>XMJPS6605Q</t>
-  </si>
-  <si>
-    <t>UDYAM-QA-44-7123405</t>
-  </si>
-  <si>
-    <t>QAMSME05</t>
-  </si>
-  <si>
-    <t>XMJPS6606Q</t>
-  </si>
-  <si>
-    <t>UDYAM-QA-44-7123406</t>
-  </si>
-  <si>
-    <t>QAMSME06</t>
-  </si>
-  <si>
-    <t>XMJPS6607Q</t>
-  </si>
-  <si>
-    <t>UDYAM-QA-44-7123407</t>
-  </si>
-  <si>
-    <t>QAMSME07</t>
-  </si>
-  <si>
-    <t>XMJPS6608Q</t>
-  </si>
-  <si>
     <t>UDYAM-QA-44-7123408</t>
   </si>
   <si>
-    <t>QAMSME08</t>
+    <t>Acust08</t>
+  </si>
+  <si>
+    <t>Aloan08</t>
   </si>
   <si>
     <t>XMJPS6609Q</t>
@@ -236,7 +263,10 @@
     <t>UDYAM-QA-44-7123409</t>
   </si>
   <si>
-    <t>QAMSME09</t>
+    <t>Acust09</t>
+  </si>
+  <si>
+    <t>Aloan09</t>
   </si>
   <si>
     <t>XMJPS6610Q</t>
@@ -245,7 +275,10 @@
     <t>UDYAM-QA-44-7123410</t>
   </si>
   <si>
-    <t>QAMSME10</t>
+    <t>Acust10</t>
+  </si>
+  <si>
+    <t>Aloan10</t>
   </si>
   <si>
     <t>XMJPS6611Q</t>
@@ -254,19 +287,22 @@
     <t>UDYAM-QA-44-7123411</t>
   </si>
   <si>
-    <t>QAMSME11</t>
+    <t>Acust11</t>
+  </si>
+  <si>
+    <t>Aloan11</t>
   </si>
   <si>
     <t>XMJPS6612Q</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>UDYAM-QA-44-7123412</t>
   </si>
   <si>
-    <t>QAMSME12</t>
+    <t>Acust12</t>
+  </si>
+  <si>
+    <t>Aloan12</t>
   </si>
   <si>
     <t>XMJPS6613Q</t>
@@ -275,7 +311,10 @@
     <t>UDYAM-QA-44-7123413</t>
   </si>
   <si>
-    <t>QAMSME13</t>
+    <t>Acust13</t>
+  </si>
+  <si>
+    <t>Aloan13</t>
   </si>
   <si>
     <t>XMJPS6614Q</t>
@@ -284,7 +323,10 @@
     <t>UDYAM-QA-44-7123414</t>
   </si>
   <si>
-    <t>QAMSME14</t>
+    <t>Acust14</t>
+  </si>
+  <si>
+    <t>Aloan14</t>
   </si>
   <si>
     <t>XMJPS6615Q</t>
@@ -293,7 +335,10 @@
     <t>UDYAM-QA-44-7123415</t>
   </si>
   <si>
-    <t>QAMSME15</t>
+    <t>Acust15</t>
+  </si>
+  <si>
+    <t>Aloan15</t>
   </si>
   <si>
     <t>XMJPS6616Q</t>
@@ -302,7 +347,10 @@
     <t>UDYAM-QA-44-7123416</t>
   </si>
   <si>
-    <t>QAMSME16</t>
+    <t>Acust16</t>
+  </si>
+  <si>
+    <t>Aloan16</t>
   </si>
   <si>
     <t>XMJPS6617Q</t>
@@ -311,7 +359,10 @@
     <t>UDYAM-QA-44-7123417</t>
   </si>
   <si>
-    <t>QAMSME17</t>
+    <t>Acust17</t>
+  </si>
+  <si>
+    <t>Aloan17</t>
   </si>
   <si>
     <t>XMJPS6618Q</t>
@@ -320,7 +371,10 @@
     <t>UDYAM-QA-44-7123418</t>
   </si>
   <si>
-    <t>QAMSME18</t>
+    <t>Acust18</t>
+  </si>
+  <si>
+    <t>Aloan18</t>
   </si>
   <si>
     <t>XMJPS6619Q</t>
@@ -329,7 +383,10 @@
     <t>UDYAM-QA-44-7123419</t>
   </si>
   <si>
-    <t>QAMSME19</t>
+    <t>Acust19</t>
+  </si>
+  <si>
+    <t>Aloan19</t>
   </si>
   <si>
     <t>XMJPS6620Q</t>
@@ -338,7 +395,58 @@
     <t>UDYAM-QA-44-7123420</t>
   </si>
   <si>
-    <t>QAMSME20</t>
+    <t>Acust20</t>
+  </si>
+  <si>
+    <t>Aloan20</t>
+  </si>
+  <si>
+    <t>XMJPS6621Q</t>
+  </si>
+  <si>
+    <t>UDYAM-QA-44-7123421</t>
+  </si>
+  <si>
+    <t>Acust21</t>
+  </si>
+  <si>
+    <t>Aloan21</t>
+  </si>
+  <si>
+    <t>XMJPS6622Q</t>
+  </si>
+  <si>
+    <t>UDYAM-QA-44-7123422</t>
+  </si>
+  <si>
+    <t>Acust22</t>
+  </si>
+  <si>
+    <t>Aloan22</t>
+  </si>
+  <si>
+    <t>XMJPS6623Q</t>
+  </si>
+  <si>
+    <t>UDYAM-QA-44-7123423</t>
+  </si>
+  <si>
+    <t>Acust23</t>
+  </si>
+  <si>
+    <t>Aloan23</t>
+  </si>
+  <si>
+    <t>XMJPS6624Q</t>
+  </si>
+  <si>
+    <t>UDYAM-QA-44-7123424</t>
+  </si>
+  <si>
+    <t>Acust24</t>
+  </si>
+  <si>
+    <t>Aloan24</t>
   </si>
 </sst>
 </file>
@@ -351,7 +459,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +474,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -852,134 +966,134 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -997,11 +1111,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1323,7 +1434,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.1428571428571" style="1" customWidth="1"/>
@@ -1462,17 +1573,17 @@
       <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="6">
         <v>1</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="7">
-        <v>3</v>
+      <c r="J2" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K2" s="1">
         <v>1</v>
@@ -1481,40 +1592,40 @@
         <v>1</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="1">
         <v>201009</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T2" s="1">
         <v>7.5</v>
       </c>
-      <c r="U2">
-        <v>1000000000</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>38</v>
+      <c r="U2" s="6">
+        <v>300000000</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W2" s="1">
         <v>48</v>
       </c>
       <c r="X2" s="6">
-        <v>450000000</v>
+        <v>50000000</v>
       </c>
       <c r="Y2" s="8">
         <v>1</v>
@@ -1525,16 +1636,16 @@
       <c r="AA2" s="1">
         <v>24</v>
       </c>
-      <c r="AB2" s="6" t="s">
-        <v>39</v>
+      <c r="AB2" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>30</v>
@@ -1548,17 +1659,17 @@
       <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="6">
         <v>1</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="7">
-        <v>1</v>
+      <c r="I3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
@@ -1567,34 +1678,34 @@
         <v>1</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q3" s="1">
         <v>201009</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T3" s="1">
         <v>7.5</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="6">
         <v>1000000000</v>
       </c>
-      <c r="V3" s="6" t="s">
-        <v>38</v>
+      <c r="V3" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W3" s="1">
         <v>48</v>
@@ -1611,16 +1722,16 @@
       <c r="AA3" s="1">
         <v>24</v>
       </c>
-      <c r="AB3" s="6" t="s">
-        <v>39</v>
+      <c r="AB3" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>30</v>
@@ -1634,17 +1745,17 @@
       <c r="F4" s="1">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
-        <v>2</v>
+      <c r="G4" s="6">
+        <v>1</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="7">
-        <v>3</v>
+      <c r="I4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
@@ -1653,40 +1764,40 @@
         <v>1</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q4" s="1">
         <v>201009</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="T4" s="1">
         <v>7.5</v>
       </c>
       <c r="U4" s="6">
-        <v>200000000</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>38</v>
+        <v>500000000</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W4" s="1">
         <v>48</v>
       </c>
       <c r="X4" s="6">
-        <v>50000000</v>
+        <v>150000000</v>
       </c>
       <c r="Y4" s="8">
         <v>1</v>
@@ -1697,16 +1808,16 @@
       <c r="AA4" s="1">
         <v>24</v>
       </c>
-      <c r="AB4" s="6" t="s">
-        <v>39</v>
+      <c r="AB4" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>30</v>
@@ -1720,17 +1831,17 @@
       <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>50</v>
+      <c r="G5" s="6">
+        <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="7">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
@@ -1739,40 +1850,40 @@
         <v>1</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q5" s="1">
         <v>201009</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="T5" s="1">
         <v>7.5</v>
       </c>
       <c r="U5" s="6">
-        <v>100000000</v>
-      </c>
-      <c r="V5" s="6" t="s">
-        <v>38</v>
+        <v>500000000</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W5" s="1">
         <v>48</v>
       </c>
       <c r="X5" s="6">
-        <v>50000000</v>
+        <v>450000000</v>
       </c>
       <c r="Y5" s="8">
         <v>1</v>
@@ -1783,8 +1894,8 @@
       <c r="AA5" s="1">
         <v>24</v>
       </c>
-      <c r="AB5" s="6" t="s">
-        <v>39</v>
+      <c r="AB5" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -1792,7 +1903,7 @@
         <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>30</v>
@@ -1806,17 +1917,17 @@
       <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="6">
         <v>1</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" s="7">
-        <v>1</v>
+      <c r="I6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -1825,40 +1936,40 @@
         <v>1</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="1">
         <v>201009</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T6" s="1">
         <v>7.5</v>
       </c>
-      <c r="U6">
-        <v>1000000000</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>38</v>
+      <c r="U6" s="6">
+        <v>600000000</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W6" s="1">
         <v>48</v>
       </c>
       <c r="X6" s="6">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="8">
         <v>1</v>
@@ -1869,16 +1980,16 @@
       <c r="AA6" s="1">
         <v>24</v>
       </c>
-      <c r="AB6" s="6" t="s">
-        <v>39</v>
+      <c r="AB6" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>30</v>
@@ -1892,17 +2003,17 @@
       <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="6">
         <v>1</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="7">
-        <v>3</v>
+      <c r="I7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -1911,40 +2022,40 @@
         <v>1</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q7" s="1">
         <v>201009</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="T7" s="1">
         <v>7.5</v>
       </c>
-      <c r="U7">
-        <v>1000000000</v>
-      </c>
-      <c r="V7" s="6" t="s">
-        <v>38</v>
+      <c r="U7" s="6">
+        <v>500000000</v>
+      </c>
+      <c r="V7" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W7" s="1">
         <v>48</v>
       </c>
       <c r="X7" s="6">
-        <v>50000000</v>
+        <v>450000000</v>
       </c>
       <c r="Y7" s="8">
         <v>1</v>
@@ -1955,16 +2066,16 @@
       <c r="AA7" s="1">
         <v>24</v>
       </c>
-      <c r="AB7" s="6" t="s">
-        <v>39</v>
+      <c r="AB7" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>30</v>
@@ -1978,17 +2089,17 @@
       <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="6">
         <v>2</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="7">
-        <v>1</v>
+      <c r="I8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
@@ -1997,34 +2108,34 @@
         <v>1</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="1">
         <v>201009</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="T8" s="1">
         <v>7.5</v>
       </c>
       <c r="U8" s="6">
-        <v>180000000</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>38</v>
+        <v>200000000</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W8" s="1">
         <v>48</v>
@@ -2041,16 +2152,16 @@
       <c r="AA8" s="1">
         <v>24</v>
       </c>
-      <c r="AB8" s="6" t="s">
-        <v>39</v>
+      <c r="AB8" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>30</v>
@@ -2064,17 +2175,17 @@
       <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>50</v>
+      <c r="G9" s="6">
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" s="7">
-        <v>3</v>
+        <v>71</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
@@ -2083,40 +2194,40 @@
         <v>1</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q9" s="1">
         <v>201009</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="T9" s="1">
         <v>7.5</v>
       </c>
       <c r="U9" s="6">
-        <v>150000000</v>
-      </c>
-      <c r="V9" s="6" t="s">
-        <v>38</v>
+        <v>100000000</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W9" s="1">
         <v>48</v>
       </c>
       <c r="X9" s="6">
-        <v>450000000</v>
+        <v>50000000</v>
       </c>
       <c r="Y9" s="8">
         <v>1</v>
@@ -2127,8 +2238,8 @@
       <c r="AA9" s="1">
         <v>24</v>
       </c>
-      <c r="AB9" s="6" t="s">
-        <v>39</v>
+      <c r="AB9" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -2136,7 +2247,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>30</v>
@@ -2150,17 +2261,17 @@
       <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="2">
-        <v>1</v>
+      <c r="G10" s="6">
+        <v>2</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="7">
-        <v>1</v>
+      <c r="I10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
@@ -2169,40 +2280,40 @@
         <v>1</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q10" s="1">
         <v>201009</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="T10" s="1">
         <v>7.5</v>
       </c>
-      <c r="U10">
-        <v>1000000000</v>
-      </c>
-      <c r="V10" s="6" t="s">
-        <v>38</v>
+      <c r="U10" s="6">
+        <v>150000000</v>
+      </c>
+      <c r="V10" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W10" s="1">
         <v>48</v>
       </c>
       <c r="X10" s="6">
-        <v>450000000</v>
+        <v>50000000</v>
       </c>
       <c r="Y10" s="8">
         <v>1</v>
@@ -2213,16 +2324,16 @@
       <c r="AA10" s="1">
         <v>24</v>
       </c>
-      <c r="AB10" s="6" t="s">
-        <v>39</v>
+      <c r="AB10" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>30</v>
@@ -2236,17 +2347,17 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="2">
-        <v>1</v>
+      <c r="G11" s="6">
+        <v>2</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="7">
-        <v>1</v>
+      <c r="I11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
@@ -2255,34 +2366,34 @@
         <v>1</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q11" s="1">
         <v>201009</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="T11" s="1">
         <v>7.5</v>
       </c>
-      <c r="U11">
-        <v>1000000000</v>
-      </c>
-      <c r="V11" s="6" t="s">
-        <v>38</v>
+      <c r="U11" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="V11" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W11" s="1">
         <v>48</v>
@@ -2299,16 +2410,16 @@
       <c r="AA11" s="1">
         <v>24</v>
       </c>
-      <c r="AB11" s="6" t="s">
-        <v>39</v>
+      <c r="AB11" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>30</v>
@@ -2322,17 +2433,17 @@
       <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="6">
         <v>2</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J12" s="7">
-        <v>3</v>
+      <c r="I12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
@@ -2341,34 +2452,34 @@
         <v>1</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q12" s="1">
         <v>201009</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="T12" s="1">
         <v>7.5</v>
       </c>
       <c r="U12" s="6">
-        <v>200000000</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>38</v>
+        <v>180000000</v>
+      </c>
+      <c r="V12" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W12" s="1">
         <v>48</v>
@@ -2385,16 +2496,16 @@
       <c r="AA12" s="1">
         <v>24</v>
       </c>
-      <c r="AB12" s="6" t="s">
-        <v>39</v>
+      <c r="AB12" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>30</v>
@@ -2408,17 +2519,17 @@
       <c r="F13" s="1">
         <v>1</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>50</v>
+      <c r="G13" s="6">
+        <v>2</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="J13" s="7">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
@@ -2427,40 +2538,40 @@
         <v>1</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q13" s="1">
         <v>201009</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="T13" s="1">
         <v>7.5</v>
       </c>
       <c r="U13" s="6">
-        <v>200000000</v>
-      </c>
-      <c r="V13" s="6" t="s">
-        <v>38</v>
+        <v>20000000</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W13" s="1">
         <v>48</v>
       </c>
       <c r="X13" s="6">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="8">
         <v>1</v>
@@ -2471,8 +2582,8 @@
       <c r="AA13" s="1">
         <v>24</v>
       </c>
-      <c r="AB13" s="6" t="s">
-        <v>39</v>
+      <c r="AB13" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -2480,7 +2591,7 @@
         <v>28</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>30</v>
@@ -2494,17 +2605,17 @@
       <c r="F14" s="1">
         <v>1</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="6">
         <v>1</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J14" s="7">
-        <v>3</v>
+      <c r="I14" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
@@ -2513,34 +2624,34 @@
         <v>1</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q14" s="1">
         <v>201009</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="T14" s="1">
         <v>7.5</v>
       </c>
-      <c r="U14">
-        <v>1000000000</v>
-      </c>
-      <c r="V14" s="6" t="s">
-        <v>38</v>
+      <c r="U14" s="6">
+        <v>300000000</v>
+      </c>
+      <c r="V14" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W14" s="1">
         <v>48</v>
@@ -2557,16 +2668,16 @@
       <c r="AA14" s="1">
         <v>24</v>
       </c>
-      <c r="AB14" s="6" t="s">
-        <v>39</v>
+      <c r="AB14" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>30</v>
@@ -2580,17 +2691,17 @@
       <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="6">
         <v>1</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="J15" s="7">
-        <v>1</v>
+      <c r="I15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
@@ -2599,40 +2710,40 @@
         <v>1</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q15" s="1">
         <v>201009</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="T15" s="1">
         <v>7.5</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="6">
         <v>1000000000</v>
       </c>
-      <c r="V15" s="6" t="s">
-        <v>38</v>
+      <c r="V15" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W15" s="1">
         <v>48</v>
       </c>
       <c r="X15" s="6">
-        <v>50000000</v>
+        <v>450000000</v>
       </c>
       <c r="Y15" s="8">
         <v>1</v>
@@ -2643,16 +2754,16 @@
       <c r="AA15" s="1">
         <v>24</v>
       </c>
-      <c r="AB15" s="6" t="s">
-        <v>39</v>
+      <c r="AB15" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>30</v>
@@ -2666,17 +2777,17 @@
       <c r="F16" s="1">
         <v>1</v>
       </c>
-      <c r="G16" s="2">
-        <v>2</v>
+      <c r="G16" s="6">
+        <v>1</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="7">
-        <v>1</v>
+      <c r="I16" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
@@ -2685,40 +2796,40 @@
         <v>1</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q16" s="1">
         <v>201009</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="T16" s="1">
         <v>7.5</v>
       </c>
       <c r="U16" s="6">
-        <v>100000000</v>
-      </c>
-      <c r="V16" s="6" t="s">
-        <v>38</v>
+        <v>500000000</v>
+      </c>
+      <c r="V16" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W16" s="1">
         <v>48</v>
       </c>
       <c r="X16" s="6">
-        <v>450000000</v>
+        <v>150000000</v>
       </c>
       <c r="Y16" s="8">
         <v>1</v>
@@ -2729,16 +2840,16 @@
       <c r="AA16" s="1">
         <v>24</v>
       </c>
-      <c r="AB16" s="6" t="s">
-        <v>39</v>
+      <c r="AB16" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>30</v>
@@ -2752,17 +2863,17 @@
       <c r="F17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="9" t="s">
-        <v>50</v>
+      <c r="G17" s="6">
+        <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J17" s="7">
-        <v>3</v>
+        <v>33</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
@@ -2771,34 +2882,34 @@
         <v>1</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q17" s="1">
         <v>201009</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="T17" s="1">
         <v>7.5</v>
       </c>
       <c r="U17" s="6">
-        <v>200000000</v>
-      </c>
-      <c r="V17" s="6" t="s">
-        <v>38</v>
+        <v>500000000</v>
+      </c>
+      <c r="V17" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W17" s="1">
         <v>48</v>
@@ -2815,8 +2926,8 @@
       <c r="AA17" s="1">
         <v>24</v>
       </c>
-      <c r="AB17" s="6" t="s">
-        <v>39</v>
+      <c r="AB17" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:28">
@@ -2824,7 +2935,7 @@
         <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>30</v>
@@ -2838,17 +2949,17 @@
       <c r="F18" s="1">
         <v>1</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="6">
         <v>1</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="J18" s="7">
-        <v>1</v>
+      <c r="I18" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
@@ -2857,40 +2968,40 @@
         <v>1</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q18" s="1">
         <v>201009</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="T18" s="1">
         <v>7.5</v>
       </c>
-      <c r="U18">
-        <v>1000000000</v>
-      </c>
-      <c r="V18" s="6" t="s">
-        <v>38</v>
+      <c r="U18" s="6">
+        <v>600000000</v>
+      </c>
+      <c r="V18" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W18" s="1">
         <v>48</v>
       </c>
       <c r="X18" s="6">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="8">
         <v>1</v>
@@ -2901,16 +3012,16 @@
       <c r="AA18" s="1">
         <v>24</v>
       </c>
-      <c r="AB18" s="6" t="s">
-        <v>39</v>
+      <c r="AB18" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:28">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>30</v>
@@ -2924,17 +3035,17 @@
       <c r="F19" s="1">
         <v>1</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="6">
         <v>1</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="J19" s="7">
-        <v>3</v>
+      <c r="I19" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
@@ -2943,40 +3054,40 @@
         <v>1</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q19" s="1">
         <v>201009</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="T19" s="1">
         <v>7.5</v>
       </c>
-      <c r="U19">
-        <v>1000000000</v>
-      </c>
-      <c r="V19" s="6" t="s">
-        <v>38</v>
+      <c r="U19" s="6">
+        <v>500000000</v>
+      </c>
+      <c r="V19" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W19" s="1">
         <v>48</v>
       </c>
       <c r="X19" s="6">
-        <v>50000000</v>
+        <v>450000000</v>
       </c>
       <c r="Y19" s="8">
         <v>1</v>
@@ -2987,16 +3098,16 @@
       <c r="AA19" s="1">
         <v>24</v>
       </c>
-      <c r="AB19" s="6" t="s">
-        <v>39</v>
+      <c r="AB19" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>30</v>
@@ -3010,17 +3121,17 @@
       <c r="F20" s="1">
         <v>1</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="6">
         <v>2</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="J20" s="7">
-        <v>1</v>
+      <c r="I20" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="K20" s="1">
         <v>1</v>
@@ -3029,34 +3140,34 @@
         <v>1</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q20" s="1">
         <v>201009</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="T20" s="1">
         <v>7.5</v>
       </c>
       <c r="U20" s="6">
-        <v>100000000</v>
-      </c>
-      <c r="V20" s="6" t="s">
-        <v>38</v>
+        <v>200000000</v>
+      </c>
+      <c r="V20" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W20" s="1">
         <v>48</v>
@@ -3073,16 +3184,16 @@
       <c r="AA20" s="1">
         <v>24</v>
       </c>
-      <c r="AB20" s="6" t="s">
-        <v>39</v>
+      <c r="AB20" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>30</v>
@@ -3096,17 +3207,17 @@
       <c r="F21" s="1">
         <v>1</v>
       </c>
-      <c r="G21" s="9" t="s">
-        <v>50</v>
+      <c r="G21" s="6">
+        <v>2</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="J21" s="7">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
@@ -3115,34 +3226,34 @@
         <v>1</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q21" s="1">
         <v>201009</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="T21" s="1">
         <v>7.5</v>
       </c>
       <c r="U21" s="6">
-        <v>180000000</v>
-      </c>
-      <c r="V21" s="6" t="s">
-        <v>38</v>
+        <v>100000000</v>
+      </c>
+      <c r="V21" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="W21" s="1">
         <v>48</v>
@@ -3159,18 +3270,355 @@
       <c r="AA21" s="1">
         <v>24</v>
       </c>
-      <c r="AB21" s="6" t="s">
-        <v>39</v>
+      <c r="AB21" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:28">
-      <c r="X22" s="6"/>
-      <c r="AB22" s="6"/>
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="1">
+        <v>9876543210</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6">
+        <v>2</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>201009</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="T22" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="U22" s="6">
+        <v>150000000</v>
+      </c>
+      <c r="V22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="W22" s="1">
+        <v>48</v>
+      </c>
+      <c r="X22" s="6">
+        <v>50000000</v>
+      </c>
+      <c r="Y22" s="8">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="8">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>24</v>
+      </c>
+      <c r="AB22" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28">
+      <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="1">
+        <v>9876543210</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6">
+        <v>2</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>201009</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T23" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="U23" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="V23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="W23" s="1">
+        <v>48</v>
+      </c>
+      <c r="X23" s="6">
+        <v>50000000</v>
+      </c>
+      <c r="Y23" s="8">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="8">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>24</v>
+      </c>
+      <c r="AB23" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28">
+      <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="1">
+        <v>9876543210</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6">
+        <v>2</v>
+      </c>
+      <c r="H24" s="1">
+        <v>3</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>201009</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="T24" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="U24" s="6">
+        <v>180000000</v>
+      </c>
+      <c r="V24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="W24" s="1">
+        <v>48</v>
+      </c>
+      <c r="X24" s="6">
+        <v>50000000</v>
+      </c>
+      <c r="Y24" s="8">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="8">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>24</v>
+      </c>
+      <c r="AB24" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28">
+      <c r="A25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9876543210</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="6">
+        <v>2</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>201009</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="T25" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="U25" s="6">
+        <v>20000000</v>
+      </c>
+      <c r="V25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="W25" s="1">
+        <v>48</v>
+      </c>
+      <c r="X25" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="8">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="8">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>24</v>
+      </c>
+      <c r="AB25" s="7" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AB21" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="test3@gmail.com"/>
     <hyperlink ref="C3" r:id="rId1" display="test3@gmail.com"/>
@@ -3192,6 +3640,10 @@
     <hyperlink ref="C13" r:id="rId1" display="test3@gmail.com"/>
     <hyperlink ref="C17" r:id="rId1" display="test3@gmail.com"/>
     <hyperlink ref="C21" r:id="rId1" display="test3@gmail.com"/>
+    <hyperlink ref="C22" r:id="rId1" display="test3@gmail.com"/>
+    <hyperlink ref="C24" r:id="rId1" display="test3@gmail.com"/>
+    <hyperlink ref="C23" r:id="rId1" display="test3@gmail.com"/>
+    <hyperlink ref="C25" r:id="rId1" display="test3@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
